--- a/Flow_Conditions.xlsx
+++ b/Flow_Conditions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E099D89D-4503-4491-9830-72C790E2E396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4152162-8511-4CCF-89B1-AEF8465FFC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8CCDB4B7-DCAF-4468-A674-5318AAC9ACE4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Phase 1</t>
   </si>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>f1 ferrari - cfd by 20048548 | SimScale...</t>
-  </si>
-  <si>
-    <t>MSES Mach for Convergence</t>
   </si>
 </sst>
 </file>
@@ -602,14 +599,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68C87D2A-5B85-4E5B-879F-5CB21C9415B4}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="18.109375" customWidth="1"/>
     <col min="12" max="12" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -643,16 +640,13 @@
       <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-5</v>
+        <v>-2.5</v>
       </c>
       <c r="C2">
         <v>115</v>
@@ -686,11 +680,8 @@
         <f>I2*E2*H2/J2</f>
         <v>907997.71493858891</v>
       </c>
-      <c r="L2">
-        <v>0.23</v>
-      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -729,36 +720,33 @@
         <f>I3*E3*H3/J3</f>
         <v>1184344.8455720723</v>
       </c>
-      <c r="L3">
-        <v>0.25</v>
-      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1" display="https://las-motorsport.com/f1/blog/average-speed-at-the-monaco-grand-prix/17236/" xr:uid="{2C32C734-BC64-4C53-943F-24EA6A126D70}"/>
-    <hyperlink ref="A7" r:id="rId2" display="https://www.researchgate.net/publication/372250505_OPTIMIZING_FORMULA_1_REAR_WINGS_WITH_NACA_SERIES_AIRFOILS_FOR_MAXIMUM_PERFORMANCE" xr:uid="{1A708796-F89D-4F4E-B0B7-AFE4169F682F}"/>
-    <hyperlink ref="A8" r:id="rId3" display="https://sakiicelimbekardas.blogspot.com/2016/02/cfd.html" xr:uid="{F1420793-9189-4994-947F-32F34A5C19D6}"/>
-    <hyperlink ref="A9" r:id="rId4" display="https://www.simscale.com/projects/20048548/f1_ferrari_-_copy/" xr:uid="{BF4090AE-D37E-4004-BE17-422218E1C2FD}"/>
+    <hyperlink ref="A7" r:id="rId1" display="https://www.researchgate.net/publication/372250505_OPTIMIZING_FORMULA_1_REAR_WINGS_WITH_NACA_SERIES_AIRFOILS_FOR_MAXIMUM_PERFORMANCE" xr:uid="{1A708796-F89D-4F4E-B0B7-AFE4169F682F}"/>
+    <hyperlink ref="A8" r:id="rId2" display="https://sakiicelimbekardas.blogspot.com/2016/02/cfd.html" xr:uid="{F1420793-9189-4994-947F-32F34A5C19D6}"/>
+    <hyperlink ref="A9" r:id="rId3" display="https://www.simscale.com/projects/20048548/f1_ferrari_-_copy/" xr:uid="{BF4090AE-D37E-4004-BE17-422218E1C2FD}"/>
+    <hyperlink ref="A6" r:id="rId4" display="https://las-motorsport.com/f1/blog/average-speed-at-the-monaco-grand-prix/17236/" xr:uid="{2C32C734-BC64-4C53-943F-24EA6A126D70}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
